--- a/Excel/MonsterBabelMythConfig.xlsx
+++ b/Excel/MonsterBabelMythConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -1580,8 +1585,8 @@
         <v>2001</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="1"/>
-        <v>2400</v>
+        <f>E10+1400</f>
+        <v>3400</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>33</v>
@@ -1624,7 +1629,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:Q5 C3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
